--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-interpretation-extension.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-interpretation-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T11:43:27+00:00</t>
+    <t>2026-07-01T12:03:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-interpretation-extension.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-interpretation-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T12:03:19+00:00</t>
+    <t>2026-07-03T07:33:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -347,7 +347,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationInterpretation-cisis|20260420150250</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationInterpretation-cisis|20260619134042</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}

--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-interpretation-extension.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-interpretation-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T07:33:59+00:00</t>
+    <t>2026-07-08T09:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-interpretation-extension.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-interpretation-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T09:43:12+00:00</t>
+    <t>2026-07-08T10:07:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
